--- a/outputs/per-fund/vc-investments-lemniscap.xlsx
+++ b/outputs/per-fund/vc-investments-lemniscap.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Only Lemniscap. The full overview with all twenty funds is in vc-investments-full.xlsx.</t>
+          <t>Only Lemniscap. The full overview with all 59 funds is in vc-investments-full.xlsx.</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>The twenty funds, with control totals per external source.</t>
+          <t>The 59 funds, with control totals per external source.</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>One row per company in which at least one of the twenty funds invested.</t>
+          <t>One row per company in which at least one of these 59 funds invested.</t>
         </is>
       </c>
     </row>
@@ -16324,11 +16324,11 @@
         <v>2</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>lemniscap, robot-ventures</t>
+          <t>arrington-capital, lemniscap, robot-ventures</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
@@ -16572,11 +16572,11 @@
         <v>0</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>1kx, lemniscap, yzi-labs</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
@@ -16759,11 +16759,11 @@
         <v>0</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>blockchain-capital, digital-currency-group, lemniscap</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
@@ -16822,11 +16822,11 @@
         <v>5</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, lemniscap, multicoin-capital</t>
+          <t>coinbase-ventures, digital-currency-group, lemniscap, multicoin-capital, parafi-capital</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
@@ -16885,11 +16885,11 @@
         <v>0</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>lemniscap, polychain</t>
+          <t>borderless-capital, lemniscap, polychain</t>
         </is>
       </c>
       <c r="M12" s="7" t="inlineStr">
@@ -16948,11 +16948,11 @@
         <v>0</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>alameda-research, arrington-capital, blockchain-capital, coinfund, lemniscap</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
@@ -17011,11 +17011,11 @@
         <v>1</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>lemniscap, polychain</t>
+          <t>1kx, lemniscap, polychain</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
@@ -17137,11 +17137,11 @@
         <v>0</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, lemniscap</t>
+          <t>coinbase-ventures, lemniscap, yzi-labs</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
@@ -17200,11 +17200,11 @@
         <v>1</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>cmt-digital, lemniscap</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
@@ -17389,11 +17389,11 @@
         <v>0</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>lemniscap, semantic-ventures</t>
+          <t>galaxy-digital, lemniscap, semantic-ventures</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
@@ -17511,11 +17511,11 @@
         <v>0</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>1kx, lemniscap</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
@@ -17572,11 +17572,11 @@
         <v>0</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>cms-holdings, lemniscap</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
@@ -17631,11 +17631,11 @@
         <v>1</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>alliance-dao, cms-holdings, hashkey-capital, lemniscap, mechanism-capital, spartan-group</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
@@ -17690,11 +17690,11 @@
         <v>0</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>lemniscap, maven11</t>
+          <t>alliance-dao, cms-holdings, hashkey-capital, lemniscap, maven11, mechanism-capital, okx-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
@@ -17753,11 +17753,11 @@
         <v>0</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>lemniscap, parafi-capital</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
@@ -17816,11 +17816,11 @@
         <v>1</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, electric-capital, lemniscap, polychain</t>
+          <t>cms-holdings, coinbase-ventures, electric-capital, lemniscap, polychain</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
@@ -17879,11 +17879,11 @@
         <v>0</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, electric-capital, framework-ventures, lemniscap, semantic-ventures</t>
+          <t>coinbase-ventures, coinfund, electric-capital, framework-ventures, hypersphere, lemniscap, semantic-ventures</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
@@ -17938,11 +17938,11 @@
         <v>4</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>alameda-research, cms-holdings, hashed, iosg-ventures, lemniscap, longhash-ventures</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
@@ -18064,11 +18064,11 @@
         <v>1</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>alameda-research, cms-holdings, lemniscap</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
@@ -18127,11 +18127,11 @@
         <v>1</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>hypersphere, lemniscap, mechanism-capital</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -18190,11 +18190,11 @@
         <v>0</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, lemniscap</t>
+          <t>delphi-ventures, lemniscap, mechanism-capital</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
@@ -18253,11 +18253,11 @@
         <v>0</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, lemniscap, polychain, robot-ventures</t>
+          <t>dragonfly, galaxy-digital, lemniscap, polychain, robot-ventures</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
@@ -18375,11 +18375,11 @@
         <v>0</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, lemniscap</t>
+          <t>delphi-ventures, gsr, lemniscap, solana-ventures</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
@@ -18438,11 +18438,11 @@
         <v>1</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>lemniscap, paradigm</t>
+          <t>cmt-digital, lemniscap, paradigm</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
@@ -18501,11 +18501,11 @@
         <v>0</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>iosg-ventures, lemniscap</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
@@ -18564,11 +18564,11 @@
         <v>0</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>animoca-brands, animoca-brands-japan, huobi-ventures, iosg-ventures, lemniscap, parafi-capital</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
@@ -18627,11 +18627,11 @@
         <v>1</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>lemniscap, polychain</t>
+          <t>alameda-research, cmt-digital, lemniscap, polychain</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
@@ -18749,11 +18749,11 @@
         <v>0</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>animoca-brands, circle-ventures, lemniscap, mechanism-capital</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
@@ -18812,11 +18812,11 @@
         <v>2</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>animoca-brands, animoca-brands-japan, lemniscap, sfermion</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
@@ -18875,11 +18875,11 @@
         <v>0</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>digital-currency-group, lemniscap, parafi-capital</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
@@ -18938,11 +18938,11 @@
         <v>1</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>hashkey-capital, lemniscap, mechanism-capital, spartan-group</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
@@ -19001,11 +19001,11 @@
         <v>3</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>alameda-research, lemniscap, solana-ventures</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
@@ -19064,11 +19064,11 @@
         <v>2</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>alameda-research, alliance-dao, lemniscap, sequoia-capital, sfermion, solana-ventures</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
@@ -19127,11 +19127,11 @@
         <v>0</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>big-brain-holdings, borderless-capital, lemniscap</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
@@ -19190,11 +19190,11 @@
         <v>0</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>gsr, lemniscap, spartan-group</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
@@ -19249,11 +19249,11 @@
         <v>2</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, lemniscap, polychain</t>
+          <t>alameda-research, amber-group, coinbase-ventures, dragonfly, jump-crypto, lemniscap, mechanism-capital, polychain</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
@@ -19438,11 +19438,11 @@
         <v>0</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>jump-crypto, lemniscap</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
@@ -19501,11 +19501,11 @@
         <v>1</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, lemniscap</t>
+          <t>framework-ventures, gsr, lemniscap</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
@@ -19566,11 +19566,11 @@
         <v>2</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, lemniscap</t>
+          <t>blockchain-capital, coinfund, figment-capital, hashed, hypersphere, lemniscap</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
@@ -19629,11 +19629,11 @@
         <v>3</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, lemniscap</t>
+          <t>dragonfly, iosg-ventures, jump-crypto, lemniscap, parafi-capital, sevenx-ventures</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
@@ -19692,11 +19692,11 @@
         <v>1</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, electric-capital, lemniscap</t>
+          <t>dragonfly, electric-capital, jump-crypto, lemniscap</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
@@ -19755,11 +19755,11 @@
         <v>1</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>cmt-digital, lemniscap, sfermion</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
@@ -19818,11 +19818,11 @@
         <v>0</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, electric-capital, framework-ventures, lemniscap</t>
+          <t>coinbase-ventures, coinfund, electric-capital, framework-ventures, galaxy-digital, jump-crypto, lemniscap</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
@@ -19881,11 +19881,11 @@
         <v>2</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, lemniscap</t>
+          <t>dragonfly, galaxy-digital, lemniscap</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
@@ -19944,11 +19944,11 @@
         <v>0</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, lemniscap</t>
+          <t>alameda-research, coinbase-ventures, dragonfly, hashed, lemniscap, polygon-ventures</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
@@ -20007,11 +20007,11 @@
         <v>3</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, delphi-ventures, lemniscap</t>
+          <t>coinbase-ventures, delphi-ventures, lemniscap, sfermion</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
@@ -20070,11 +20070,11 @@
         <v>0</v>
       </c>
       <c r="K63" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>big-brain-holdings, gsr, lemniscap</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
@@ -20133,11 +20133,11 @@
         <v>0</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>animoca-brands, animoca-brands-japan, lemniscap</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
@@ -20196,11 +20196,11 @@
         <v>0</v>
       </c>
       <c r="K65" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>digital-currency-group, lemniscap</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
@@ -20259,11 +20259,11 @@
         <v>0</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>lemniscap, robot-ventures</t>
+          <t>arrington-capital, lemniscap, parafi-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
@@ -20322,11 +20322,11 @@
         <v>0</v>
       </c>
       <c r="K67" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, lemniscap</t>
+          <t>1kx, big-brain-holdings, delphi-ventures, lemniscap, mirana-ventures</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
@@ -20385,11 +20385,11 @@
         <v>0</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, lemniscap, maven11</t>
+          <t>blockchain-capital, coinbase-ventures, lemniscap, maven11, sevenx-ventures</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
@@ -20448,11 +20448,11 @@
         <v>0</v>
       </c>
       <c r="K69" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>big-brain-holdings, lemniscap</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
@@ -20511,11 +20511,11 @@
         <v>0</v>
       </c>
       <c r="K70" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>lemniscap, multicoin-capital</t>
+          <t>circle-ventures, lemniscap, multicoin-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr">
@@ -20574,11 +20574,11 @@
         <v>0</v>
       </c>
       <c r="K71" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>lemniscap, polychain</t>
+          <t>alameda-research, lemniscap, okx-ventures, polychain</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
@@ -20637,11 +20637,11 @@
         <v>1</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>lemniscap, sfermion, yzi-labs</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr">
@@ -20700,11 +20700,11 @@
         <v>0</v>
       </c>
       <c r="K73" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>lemniscap, mirana-ventures, polygon-ventures</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
@@ -20763,11 +20763,11 @@
         <v>1</v>
       </c>
       <c r="K74" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, lemniscap, polychain</t>
+          <t>figment-capital, huobi-ventures, lemniscap, polychain</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
@@ -20820,11 +20820,11 @@
         <v>0</v>
       </c>
       <c r="K75" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>amber-group, lemniscap, mirana-ventures</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
@@ -21009,11 +21009,11 @@
         <v>1</v>
       </c>
       <c r="K78" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>cmt-digital, lemniscap</t>
         </is>
       </c>
       <c r="M78" s="7" t="inlineStr">
@@ -21135,11 +21135,11 @@
         <v>1</v>
       </c>
       <c r="K80" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, figment-capital, lemniscap, maven11, robot-ventures</t>
+          <t>1kx, delphi-ventures, figment-capital, lemniscap, maven11, robot-ventures</t>
         </is>
       </c>
       <c r="M80" s="7" t="inlineStr">
@@ -21194,11 +21194,11 @@
         <v>2</v>
       </c>
       <c r="K81" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>lemniscap, polychain</t>
+          <t>cms-holdings, lemniscap, polychain</t>
         </is>
       </c>
       <c r="M81" s="7" t="inlineStr">
@@ -21257,11 +21257,11 @@
         <v>2</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>alliance-dao, lemniscap</t>
         </is>
       </c>
       <c r="M82" s="7" t="inlineStr">
@@ -21446,11 +21446,11 @@
         <v>1</v>
       </c>
       <c r="K85" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>lemniscap, robot-ventures</t>
+          <t>gsr, lemniscap, robot-ventures</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
@@ -21509,11 +21509,11 @@
         <v>1</v>
       </c>
       <c r="K86" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>lemniscap, spartan-group</t>
         </is>
       </c>
       <c r="M86" s="7" t="inlineStr">
@@ -21635,11 +21635,11 @@
         <v>1</v>
       </c>
       <c r="K88" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>big-brain-holdings, lemniscap, sevenx-ventures</t>
         </is>
       </c>
       <c r="M88" s="7" t="inlineStr">
@@ -21759,11 +21759,11 @@
         <v>1</v>
       </c>
       <c r="K90" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>big-brain-holdings, lemniscap</t>
         </is>
       </c>
       <c r="M90" s="7" t="inlineStr">
@@ -21822,11 +21822,11 @@
         <v>2</v>
       </c>
       <c r="K91" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>hashkey-capital, lemniscap</t>
         </is>
       </c>
       <c r="M91" s="7" t="inlineStr">
@@ -21887,11 +21887,11 @@
         <v>1</v>
       </c>
       <c r="K92" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>lemniscap, mechanism-capital</t>
         </is>
       </c>
       <c r="M92" s="7" t="inlineStr">
@@ -21950,11 +21950,11 @@
         <v>1</v>
       </c>
       <c r="K93" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>lemniscap, sfermion</t>
         </is>
       </c>
       <c r="M93" s="7" t="inlineStr">
@@ -22011,11 +22011,11 @@
         <v>1</v>
       </c>
       <c r="K94" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>animoca-brands, big-brain-holdings, lemniscap, mechanism-capital, okx-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M94" s="10" t="n"/>
@@ -22135,11 +22135,11 @@
         <v>2</v>
       </c>
       <c r="K96" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, electric-capital, lemniscap</t>
+          <t>animoca-brands, coinbase-ventures, electric-capital, gsr, lemniscap, mechanism-capital</t>
         </is>
       </c>
       <c r="M96" s="7" t="inlineStr">
@@ -22261,11 +22261,11 @@
         <v>1</v>
       </c>
       <c r="K98" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, lemniscap</t>
+          <t>framework-ventures, hypersphere, lemniscap</t>
         </is>
       </c>
       <c r="M98" s="10" t="n"/>
@@ -22442,11 +22442,11 @@
         <v>2</v>
       </c>
       <c r="K101" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>lemniscap, longhash-ventures</t>
         </is>
       </c>
       <c r="M101" s="7" t="inlineStr">
@@ -22505,11 +22505,11 @@
         <v>1</v>
       </c>
       <c r="K102" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>hypersphere, lemniscap, spartan-group</t>
         </is>
       </c>
       <c r="M102" s="7" t="inlineStr">
@@ -22631,11 +22631,11 @@
         <v>1</v>
       </c>
       <c r="K104" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>borderless-capital, lemniscap</t>
         </is>
       </c>
       <c r="M104" s="7" t="inlineStr">
@@ -22820,11 +22820,11 @@
         <v>1</v>
       </c>
       <c r="K107" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>amber-group, animoca-brands, gsr, lemniscap, mirana-ventures, okx-ventures</t>
         </is>
       </c>
       <c r="M107" s="7" t="inlineStr">
@@ -23137,11 +23137,11 @@
         <v>0</v>
       </c>
       <c r="K112" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>coinfund, hypersphere, lemniscap</t>
         </is>
       </c>
       <c r="M112" s="7" t="inlineStr">
@@ -23196,11 +23196,11 @@
         <v>0</v>
       </c>
       <c r="K113" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>amber-group, animoca-brands, gsr, lemniscap, mirana-ventures, okx-ventures</t>
         </is>
       </c>
       <c r="M113" s="7" t="inlineStr">
@@ -23259,11 +23259,11 @@
         <v>1</v>
       </c>
       <c r="K114" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
-          <t>lemniscap</t>
+          <t>cms-holdings, lemniscap</t>
         </is>
       </c>
       <c r="M114" s="7" t="inlineStr">
@@ -29160,7 +29160,7 @@
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>Fondspagina toont een vast maximum aantal regels; dit is een displaylimiet en geen portefeuilletotaal.</t>
+          <t>The fund page shows a fixed maximum number of rows; this is a display limit, not a portfolio total.</t>
         </is>
       </c>
       <c r="G2" s="6" t="n"/>
@@ -29172,7 +29172,7 @@
       <c r="I2" s="6" t="n"/>
       <c r="J2" s="12" t="inlineStr">
         <is>
-          <t>Geen telling verkregen; niet geschat.</t>
+          <t>No count obtained; not estimated.</t>
         </is>
       </c>
       <c r="K2" s="6" t="n">
@@ -29180,7 +29180,7 @@
       </c>
       <c r="L2" s="12" t="inlineStr">
         <is>
-          <t>`investments` is CryptoRanks eigen telling. De zichtbare portefeuillelijst toont zonder account maar tien regels; die lijst is niet gebruikt.</t>
+          <t>`investments` is CryptoRank's own count. The visible portfolio list shows only ten rows without an account; that list was not used.</t>
         </is>
       </c>
       <c r="M2" s="6" t="n">
